--- a/histograms/histogram_Promoter__w_.xlsx
+++ b/histograms/histogram_Promoter__w_.xlsx
@@ -442,63 +442,63 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1.75</v>
+        <v>0.25</v>
       </c>
       <c r="B2" t="n">
-        <v>23206</v>
+        <v>425</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>5.25</v>
+        <v>0.75</v>
       </c>
       <c r="B3" t="n">
-        <v>1951</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>8.75</v>
+        <v>1.25</v>
       </c>
       <c r="B4" t="n">
-        <v>876</v>
+        <v>239</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12.25</v>
+        <v>1.75</v>
       </c>
       <c r="B5" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15.75</v>
+        <v>2.25</v>
       </c>
       <c r="B6" t="n">
-        <v>154</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>19.25</v>
+        <v>2.75</v>
       </c>
       <c r="B7" t="n">
-        <v>123</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>22.75</v>
+        <v>3.25</v>
       </c>
       <c r="B8" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>26.25</v>
+        <v>3.75</v>
       </c>
       <c r="B9" t="n">
         <v>0</v>
@@ -506,15 +506,15 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>29.75</v>
+        <v>4.25</v>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>33.25</v>
+        <v>4.75</v>
       </c>
       <c r="B11" t="n">
         <v>0</v>
@@ -522,23 +522,23 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>36.75</v>
+        <v>5.25</v>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>40.25</v>
+        <v>5.75</v>
       </c>
       <c r="B13" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>43.75</v>
+        <v>6.25</v>
       </c>
       <c r="B14" t="n">
         <v>0</v>
@@ -546,7 +546,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>47.25</v>
+        <v>6.75</v>
       </c>
       <c r="B15" t="n">
         <v>0</v>
@@ -554,15 +554,15 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>50.75</v>
+        <v>7.25</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>54.25</v>
+        <v>7.75</v>
       </c>
       <c r="B17" t="n">
         <v>0</v>
@@ -570,7 +570,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>57.75</v>
+        <v>8.25</v>
       </c>
       <c r="B18" t="n">
         <v>0</v>
@@ -578,7 +578,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>61.25</v>
+        <v>8.75</v>
       </c>
       <c r="B19" t="n">
         <v>0</v>
@@ -586,7 +586,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>64.75</v>
+        <v>9.25</v>
       </c>
       <c r="B20" t="n">
         <v>0</v>
@@ -594,7 +594,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>68.25</v>
+        <v>9.75</v>
       </c>
       <c r="B21" t="n">
         <v>1</v>
